--- a/Companion-Workbooks/Finding_Register_Workbook.xlsx
+++ b/Companion-Workbooks/Finding_Register_Workbook.xlsx
@@ -11,12 +11,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WELCOME" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LICENCE" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 1 Audit Program" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 2 Audit Plan" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 3 Trail Record" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 4 Sample Record" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 5 Finding Register" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 6 Closure Verification" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 6 Audit Program" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 7 Audit Plan" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 8 Trail Record" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 9 Sample Record" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 10 Finding Register" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 11 Closure Verification" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXAMPLE A Goods-in" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXAMPLE B Machining cell" sheetId="13" state="visible" r:id="rId13"/>
@@ -27,8 +27,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Cover'!$A$1:$I$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'WELCOME'!$A$1:$I$71</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'LICENCE'!$A$1:$I$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Form 1 Audit Program'!$A$4:$H$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Form 5 Finding Register'!$A$4:$Q$304</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Form 6 Audit Program'!$A$4:$H$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Form 10 Finding Register'!$A$4:$Q$304</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'Dashboard'!$A$1:$J$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="H3" s="40" t="inlineStr">
         <is>
-          <t>NF-CW2  ·  v1.0</t>
+          <t>NF-CW2  ·  v2.0</t>
         </is>
       </c>
     </row>
@@ -2503,14 +2503,14 @@
     <row r="11" ht="46" customHeight="1" s="38">
       <c r="B11" s="43" t="inlineStr">
         <is>
-          <t>Nothing to Report</t>
+          <t>The Norwood Files</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1" s="38">
       <c r="B12" s="44" t="inlineStr">
         <is>
-          <t>A Novel About Internal Audit, Evidence and the Questions Nobody Wrote Down</t>
+          <t>A Novel About Risk, Audit and Root Cause in a Factory That Stopped Pretending</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
     <row r="15" ht="26" customHeight="1" s="38">
       <c r="B15" s="45" t="inlineStr">
         <is>
-          <t>Companion to Book Two</t>
+          <t>Companion to Part Two — The Audit</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="C21" s="49" t="inlineStr">
         <is>
-          <t>v1.0  ·  NF-CW2</t>
+          <t>v2.0  ·  NF-CW2</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="C23" s="49" t="inlineStr">
         <is>
-          <t>Matches the first edition of the book (Editorial Baseline EBL-3.1)</t>
+          <t>Matches the omnibus first edition of The Norwood Files (build RC-Rev9)</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="C24" s="49" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>29 August 2026</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW2 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2795,23 +2795,23 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="38">
       <c r="A5" s="88">
-        <f>COUNTA('Form 1 Audit Program'!A5:A64)</f>
+        <f>COUNTA('Form 6 Audit Program'!A5:A64)</f>
         <v/>
       </c>
       <c r="C5" s="88">
-        <f>COUNTIF('Form 1 Audit Program'!G5:G64,"OVERDUE")</f>
+        <f>COUNTIF('Form 6 Audit Program'!G5:G64,"OVERDUE")</f>
         <v/>
       </c>
       <c r="E5" s="88">
-        <f>COUNTIF('Form 5 Finding Register'!K5:K304,"open")</f>
+        <f>COUNTIF('Form 10 Finding Register'!K5:K304,"open")</f>
         <v/>
       </c>
       <c r="G5" s="88">
-        <f>IFERROR(MAX('Form 5 Finding Register'!Q5:Q304),0)</f>
+        <f>IFERROR(MAX('Form 10 Finding Register'!Q5:Q304),0)</f>
         <v/>
       </c>
       <c r="I5" s="88">
-        <f>COUNTIF('Form 5 Finding Register'!O5:O304,"SELF-VERIFIED")</f>
+        <f>COUNTIF('Form 10 Finding Register'!O5:O304,"SELF-VERIFIED")</f>
         <v/>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="B48" s="93">
-        <f>COUNTIF('Form 1 Audit Program'!$G$5:$G$64,"OK")</f>
+        <f>COUNTIF('Form 6 Audit Program'!$G$5:$G$64,"OK")</f>
         <v/>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="B49" s="93">
-        <f>COUNTIF('Form 1 Audit Program'!$G$5:$G$64,"DUE SOON")</f>
+        <f>COUNTIF('Form 6 Audit Program'!$G$5:$G$64,"DUE SOON")</f>
         <v/>
       </c>
     </row>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="B50" s="93">
-        <f>COUNTIF('Form 1 Audit Program'!$G$5:$G$64,"OVERDUE")</f>
+        <f>COUNTIF('Form 6 Audit Program'!$G$5:$G$64,"OVERDUE")</f>
         <v/>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="B54" s="93">
-        <f>COUNTIF('Form 5 Finding Register'!$E$5:$E$304,"nonconformity")</f>
+        <f>COUNTIF('Form 10 Finding Register'!$E$5:$E$304,"nonconformity")</f>
         <v/>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="B55" s="93">
-        <f>COUNTIF('Form 5 Finding Register'!$E$5:$E$304,"observation")</f>
+        <f>COUNTIF('Form 10 Finding Register'!$E$5:$E$304,"observation")</f>
         <v/>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="B59" s="93">
-        <f>COUNTIFS('Form 5 Finding Register'!$K$5:$K$304,"open",'Form 5 Finding Register'!$L$5:$L$304,"&gt;90")</f>
+        <f>COUNTIFS('Form 10 Finding Register'!$K$5:$K$304,"open",'Form 10 Finding Register'!$L$5:$L$304,"&gt;90")</f>
         <v/>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="B60" s="93">
-        <f>COUNTIFS('Form 5 Finding Register'!$K$5:$K$304,"open",'Form 5 Finding Register'!$L$5:$L$304,"&gt;60",'Form 5 Finding Register'!$L$5:$L$304,"&lt;=90")</f>
+        <f>COUNTIFS('Form 10 Finding Register'!$K$5:$K$304,"open",'Form 10 Finding Register'!$L$5:$L$304,"&gt;60",'Form 10 Finding Register'!$L$5:$L$304,"&lt;=90")</f>
         <v/>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="B61" s="93">
-        <f>COUNTIFS('Form 5 Finding Register'!$K$5:$K$304,"open",'Form 5 Finding Register'!$L$5:$L$304,"&gt;30",'Form 5 Finding Register'!$L$5:$L$304,"&lt;=60")</f>
+        <f>COUNTIFS('Form 10 Finding Register'!$K$5:$K$304,"open",'Form 10 Finding Register'!$L$5:$L$304,"&gt;30",'Form 10 Finding Register'!$L$5:$L$304,"&lt;=60")</f>
         <v/>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="B62" s="93">
-        <f>COUNTIFS('Form 5 Finding Register'!$K$5:$K$304,"open",'Form 5 Finding Register'!$L$5:$L$304,"&lt;=30")</f>
+        <f>COUNTIFS('Form 10 Finding Register'!$K$5:$K$304,"open",'Form 10 Finding Register'!$L$5:$L$304,"&lt;=30")</f>
         <v/>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="B66" s="93">
-        <f>COUNTIF('Form 5 Finding Register'!$K$5:$K$304,"open")</f>
+        <f>COUNTIF('Form 10 Finding Register'!$K$5:$K$304,"open")</f>
         <v/>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="B67" s="93">
-        <f>COUNTIF('Form 5 Finding Register'!$K$5:$K$304,"actioned")</f>
+        <f>COUNTIF('Form 10 Finding Register'!$K$5:$K$304,"actioned")</f>
         <v/>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="B68" s="93">
-        <f>COUNTIF('Form 5 Finding Register'!$K$5:$K$304,"closed")</f>
+        <f>COUNTIF('Form 10 Finding Register'!$K$5:$K$304,"closed")</f>
         <v/>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW2 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3144,7 +3144,7 @@
     <row r="2" ht="15.75" customHeight="1" s="38">
       <c r="A2" s="70" t="inlineStr">
         <is>
-          <t>Worked audit from Part 2 of the book. Read, do not edit.</t>
+          <t>Worked audit from Part Two of the book. Read, do not edit.</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW2 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3353,7 +3353,7 @@
     <row r="2" ht="15.75" customHeight="1" s="38">
       <c r="A2" s="70" t="inlineStr">
         <is>
-          <t>Worked audit from Part 2 of the book. Read, do not edit.</t>
+          <t>Worked audit from Part Two of the book. Read, do not edit.</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW2 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3535,7 +3535,7 @@
     <row r="2" ht="15.75" customHeight="1" s="38">
       <c r="A2" s="70" t="inlineStr">
         <is>
-          <t>Worked audit from Part 2 of the book. Read, do not edit.</t>
+          <t>Worked audit from Part Two of the book. Read, do not edit.</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW2 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3719,7 +3719,7 @@
     <row r="7" ht="15" customHeight="1" s="38">
       <c r="B7" s="103" t="inlineStr">
         <is>
-          <t>Companion to Book Two</t>
+          <t>Companion to Part Two</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
     <row r="9" ht="15" customHeight="1" s="38">
       <c r="B9" s="104" t="inlineStr">
         <is>
-          <t>Document code: NF-CW2 · Identity: NBSM v1.0 · Baseline: EBL-3.1 · Issued 22 August 2026</t>
+          <t>Document code: NF-CW2 · Identity: NBSM v1.0 · Baseline: RC-Rev9 · Issued 29 August 2026</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="H2" s="40" t="inlineStr">
         <is>
-          <t>NF-CW2  ·  v1.0</t>
+          <t>NF-CW2  ·  v2.0</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
     <row r="8" ht="14" customHeight="1" s="38">
       <c r="B8" s="53" t="inlineStr">
         <is>
-          <t>This workbook is the working half of Book Two of The Norwood Files. It carries the forms from the book with the rules already written into the formulas, so that the method can be run on a real process instead of read about. Its subject is building an internal audit programme from risk rather than from the table of contents: scheduling, trails, sampling, findings that survive appeal, and closure.</t>
+          <t>This workbook is the working half of Part Two of The Norwood Files. It carries the forms from the book with the rules already written into the formulas, so that the method can be run on a real process instead of read about. Its subject is building an internal audit program from risk rather than from the table of contents: scheduling, trails, sampling, findings that survive appeal, and closure.</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
     <row r="21" ht="14" customHeight="1" s="38">
       <c r="B21" s="53" t="inlineStr">
         <is>
-          <t>The numbered sheets carry the same Form numbers as the book. Form 3 in the book is Form 3 in this file. The sheets prefixed EXAMPLE are the worked cases from the book, complete and populated, so that you can see how a row behaves before you clear it and start on your own process.</t>
+          <t>The numbered sheets carry the same Form numbers as the book. Form 8 in the book is Form 8 in this file. The sheets prefixed EXAMPLE are the worked cases from the book, complete and populated, so that you can see how a row behaves before you clear it and start on your own process.</t>
         </is>
       </c>
     </row>
@@ -3996,12 +3996,12 @@
     <row r="42" ht="28" customHeight="1" s="38">
       <c r="B42" s="57" t="inlineStr">
         <is>
-          <t>Form 1 Audit Program</t>
+          <t>Form 6 Audit Program</t>
         </is>
       </c>
       <c r="C42" s="58" t="inlineStr">
         <is>
-          <t>The annual programme built from the register and the nonconformance log, with a “why now” against every row.</t>
+          <t>The annual program built from the register and the nonconformance log, with a “why now” against every row.</t>
         </is>
       </c>
       <c r="D42" s="47" t="n"/>
@@ -4013,7 +4013,7 @@
     <row r="43" ht="28" customHeight="1" s="38">
       <c r="B43" s="57" t="inlineStr">
         <is>
-          <t>Form 2 Audit Plan</t>
+          <t>Form 7 Audit Plan</t>
         </is>
       </c>
       <c r="C43" s="58" t="inlineStr">
@@ -4030,7 +4030,7 @@
     <row r="44" ht="28" customHeight="1" s="38">
       <c r="B44" s="57" t="inlineStr">
         <is>
-          <t>Form 3 Trail Record</t>
+          <t>Form 8 Trail Record</t>
         </is>
       </c>
       <c r="C44" s="58" t="inlineStr">
@@ -4047,7 +4047,7 @@
     <row r="45" ht="28" customHeight="1" s="38">
       <c r="B45" s="57" t="inlineStr">
         <is>
-          <t>Form 4 Sample Record</t>
+          <t>Form 9 Sample Record</t>
         </is>
       </c>
       <c r="C45" s="58" t="inlineStr">
@@ -4064,7 +4064,7 @@
     <row r="46" ht="28" customHeight="1" s="38">
       <c r="B46" s="57" t="inlineStr">
         <is>
-          <t>Form 5 Finding Register</t>
+          <t>Form 10 Finding Register</t>
         </is>
       </c>
       <c r="C46" s="58" t="inlineStr">
@@ -4081,7 +4081,7 @@
     <row r="47" ht="28" customHeight="1" s="38">
       <c r="B47" s="57" t="inlineStr">
         <is>
-          <t>Form 6 Closure Verification</t>
+          <t>Form 11 Closure Verification</t>
         </is>
       </c>
       <c r="C47" s="58" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="C48" s="58" t="inlineStr">
         <is>
-          <t>Programme coverage and finding status.</t>
+          <t>Program coverage and finding status.</t>
         </is>
       </c>
       <c r="D48" s="47" t="n"/>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="H2" s="40" t="inlineStr">
         <is>
-          <t>NF-CW2  ·  v1.0</t>
+          <t>NF-CW2  ·  v2.0</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       <c r="C9" s="47" t="n"/>
       <c r="D9" s="65" t="inlineStr">
         <is>
-          <t>The Norwood Files — Companion to Book Two</t>
+          <t>The Norwood Files — Companion to Part Two</t>
         </is>
       </c>
       <c r="E9" s="47" t="n"/>
@@ -4385,7 +4385,7 @@
       <c r="C10" s="47" t="n"/>
       <c r="D10" s="65" t="inlineStr">
         <is>
-          <t>Nothing to Report</t>
+          <t>The Norwood Files</t>
         </is>
       </c>
       <c r="E10" s="47" t="n"/>
@@ -4419,7 +4419,7 @@
       <c r="C12" s="47" t="n"/>
       <c r="D12" s="65" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v2.0</t>
         </is>
       </c>
       <c r="E12" s="47" t="n"/>
@@ -4436,7 +4436,7 @@
       <c r="C13" s="47" t="n"/>
       <c r="D13" s="65" t="inlineStr">
         <is>
-          <t>v1.0  ·  issued 22 August 2026</t>
+          <t>v2.0  ·  issued 29 August 2026</t>
         </is>
       </c>
       <c r="E13" s="47" t="n"/>
@@ -4470,7 +4470,7 @@
       <c r="C15" s="47" t="n"/>
       <c r="D15" s="65" t="inlineStr">
         <is>
-          <t>EBL-3.1</t>
+          <t>RC-Rev9</t>
         </is>
       </c>
       <c r="E15" s="47" t="n"/>
@@ -4544,7 +4544,7 @@
     <row r="27" ht="13" customHeight="1" s="38">
       <c r="B27" s="66" t="inlineStr">
         <is>
-          <t>This workbook accompanies Nothing to Report and is supplied free of charge with the book. You may use it, adapt it and reproduce it inside your own organization for your own quality management system.</t>
+          <t>This workbook accompanies The Norwood Files and is supplied free of charge with the book. You may use it, adapt it and reproduce it inside your own organization for your own quality management system.</t>
         </is>
       </c>
     </row>
@@ -4645,14 +4645,14 @@
     <row r="1" ht="25.5" customHeight="1" s="38">
       <c r="A1" s="69" t="inlineStr">
         <is>
-          <t>NOTHING TO REPORT—COMPANION WORKBOOK</t>
+          <t>THE NORWOOD FILES — PART TWO COMPANION</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="38">
       <c r="A2" s="70" t="inlineStr">
         <is>
-          <t>The forms from Part 3. Free, no sign-up. Everything here is also printed in the book.</t>
+          <t>The forms from Part Five. Free, no sign-up. Everything here is also printed in the book.</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
     <row r="5" ht="25.5" customHeight="1" s="38">
       <c r="B5" s="72" t="inlineStr">
         <is>
-          <t>The audit program, plan, trail record, sample record, finding register and closure verification from Part 3, plus the three worked audits from Part 2.</t>
+          <t>The audit program, plan, trail record, sample record, finding register and closure verification from Part Five, plus the three worked audits from Part Two.</t>
         </is>
       </c>
     </row>
@@ -4688,35 +4688,35 @@
     <row r="8" ht="39" customHeight="1" s="38">
       <c r="B8" s="72" t="inlineStr">
         <is>
-          <t>1.  Build 'Form 1 Audit Program' from your process flow, your risk register and your nonconformance log. Not from the clauses. The 'why now' column is the one an external auditor asks about.</t>
+          <t>1.  Build 'Form 6 Audit Program' from your process flow, your risk register and your nonconformance log. Not from the clauses. The 'why now' column is the one an external auditor asks about.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="25.5" customHeight="1" s="38">
       <c r="B9" s="72" t="inlineStr">
         <is>
-          <t>2.  For each audit, complete 'Form 2 Audit Plan' BEFORE you open anything. The sample design goes in the plan, not at the cabinet.</t>
+          <t>2.  For each audit, complete 'Form 7 Audit Plan' BEFORE you open anything. The sample design goes in the plan, not at the cabinet.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="38">
       <c r="B10" s="72" t="inlineStr">
         <is>
-          <t>3.  Use 'Form 3 Trail Record' on the floor. One unit, forward and backward.</t>
+          <t>3.  Use 'Form 8 Trail Record' on the floor. One unit, forward and backward.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="25.5" customHeight="1" s="38">
       <c r="B11" s="72" t="inlineStr">
         <is>
-          <t>4.  Every finding goes on 'Form 5 Finding Register' in three parts: requirement, evidence, gap. No name, no department, no recommendation.</t>
+          <t>4.  Every finding goes on 'Form 10 Finding Register' in three parts: requirement, evidence, gap. No name, no department, no recommendation.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="25.5" customHeight="1" s="38">
       <c r="B12" s="72" t="inlineStr">
         <is>
-          <t>5.  'Form 6 Closure Verification' is completed by somebody other than the person who raised the finding. The register flags it if they are the same.</t>
+          <t>5.  'Form 11 Closure Verification' is completed by somebody other than the person who raised the finding. The register flags it if they are the same.</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
     <row r="18" ht="39" customHeight="1" s="38">
       <c r="B18" s="72" t="inlineStr">
         <is>
-          <t>The three sheets prefixed EXAMPLE are the worked audits from Part 2—the plan, the sample design and every finding. Read the one closest to what you have been asked to audit, then work in the blank forms. An audit program copied from this file audits somebody else’s plant.</t>
+          <t>The three sheets prefixed EXAMPLE are the worked audits from Part Two—the plan, the sample design and every finding. Read the one closest to what you have been asked to audit, then work in the blank forms. An audit program copied from this file audits somebody else’s plant.</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4780,7 @@
     <row r="22" ht="15" customHeight="1" s="38">
       <c r="A22" s="73" t="inlineStr">
         <is>
-          <t>The Norwood Files · Companion to Book Two · v1.0 · issued 22 August 2026 · matches the first edition (Editorial Baseline EBL-3.1)</t>
+          <t>The Norwood Files · Companion to Part Two · v2.0 · issued 29 August 2026 · matches the omnibus first edition (build RC-Rev9)</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4795,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW2 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5867,7 +5867,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW2 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5995,7 +5995,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW2 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -6318,7 +6318,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW2 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -6414,7 +6414,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW2 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -14997,7 +14997,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW2 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Two&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
